--- a/Result/checksun/農業科技業.xlsx
+++ b/Result/checksun/農業科技業.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1897,11 +1897,15 @@
           <t>16.705</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>17.18</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>17.48</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>17.18</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>17.48</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2654,7 +2658,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2669,7 +2673,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -2679,12 +2683,12 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2883,11 +2887,15 @@
           <t>16.76</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>17.24</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>17.47</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>17.24</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3640,7 +3648,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3655,7 +3663,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -3665,12 +3673,12 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3869,11 +3877,15 @@
           <t>16.81</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>17.47</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>17.32</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4626,7 +4638,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -4641,7 +4653,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -4651,12 +4663,12 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4855,11 +4867,15 @@
           <t>16.875</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>17.46</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>17.46</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5612,7 +5628,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -5627,7 +5643,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -5637,12 +5653,12 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5841,11 +5857,15 @@
           <t>16.975</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>17.45</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>17.47</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>17.45</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6598,7 +6618,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -6613,22 +6633,22 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6827,11 +6847,15 @@
           <t>17.06</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>17.53</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>17.45</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>17.53</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>17.45</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7584,7 +7608,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7599,22 +7623,22 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7813,11 +7837,15 @@
           <t>17.175</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>17.59</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>17.46</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>17.59</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>17.46</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8570,7 +8598,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -8585,22 +8613,22 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8799,11 +8827,15 @@
           <t>17.26</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>17.64</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>17.44</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>17.64</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>17.44</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9556,7 +9588,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -9571,22 +9603,22 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9785,11 +9817,15 @@
           <t>17.38</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>17.71</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>17.43</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>17.71</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>17.43</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10522,57 +10558,57 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10771,11 +10807,15 @@
           <t>27.215</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>26.32</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>26.19</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>26.32</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>26.19</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -11508,57 +11548,57 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -11757,11 +11797,15 @@
           <t>27.09</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>26.29</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>26.2</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>26.29</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>26.2</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -12489,37 +12533,37 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -12529,22 +12573,22 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -12743,11 +12787,15 @@
           <t>26.865</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>26.24</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>26.18</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>26.24</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>26.18</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -13475,62 +13523,62 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -13729,11 +13777,15 @@
           <t>26.67</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>26.16</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>26.18</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>26.16</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -14466,17 +14518,17 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -14486,37 +14538,37 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AW15" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -14715,11 +14767,15 @@
           <t>26.48</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>26.14</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>26.13</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>26.14</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>26.13</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -15447,22 +15503,22 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -15472,24 +15528,24 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AW16" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ16" t="inlineStr">
         <is>
           <t>3.0</t>
@@ -15497,12 +15553,12 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -15701,11 +15757,15 @@
           <t>26.265</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>26.08</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>26.1</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>26.08</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -16433,22 +16493,22 @@
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -16458,37 +16518,37 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AW17" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AY17" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -16687,11 +16747,15 @@
           <t>26.045</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>26.02</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>26.07</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>26.02</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>26.07</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -17419,22 +17483,22 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -17444,7 +17508,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -17459,22 +17523,22 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -17673,11 +17737,15 @@
           <t>25.735</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>25.86</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>26</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>25.86</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18425,12 +18493,12 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -18445,22 +18513,22 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -18659,11 +18727,15 @@
           <t>25.41</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>25.92</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>25.92</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
@@ -19416,7 +19488,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -19431,7 +19503,7 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -19441,12 +19513,12 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -19645,11 +19717,15 @@
           <t>16.405</t>
         </is>
       </c>
-      <c r="CQ20" t="n">
-        <v>16.46</v>
-      </c>
-      <c r="CR20" t="n">
-        <v>16.99</v>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>16.46</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>16.99</t>
+        </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
@@ -20402,7 +20478,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -20417,7 +20493,7 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
@@ -20427,12 +20503,12 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -20631,11 +20707,15 @@
           <t>16.4</t>
         </is>
       </c>
-      <c r="CQ21" t="n">
-        <v>16.48</v>
-      </c>
-      <c r="CR21" t="n">
-        <v>17.05</v>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>16.48</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>17.05</t>
+        </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
@@ -21388,7 +21468,7 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -21403,7 +21483,7 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -21413,12 +21493,12 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
@@ -21617,11 +21697,15 @@
           <t>16.38</t>
         </is>
       </c>
-      <c r="CQ22" t="n">
-        <v>16.52</v>
-      </c>
-      <c r="CR22" t="n">
-        <v>17.09</v>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>16.52</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>17.09</t>
+        </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
@@ -22374,7 +22458,7 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
@@ -22389,7 +22473,7 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
@@ -22399,12 +22483,12 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
@@ -22603,11 +22687,15 @@
           <t>16.35</t>
         </is>
       </c>
-      <c r="CQ23" t="n">
-        <v>16.55</v>
-      </c>
-      <c r="CR23" t="n">
-        <v>17.15</v>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>16.55</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>17.15</t>
+        </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
@@ -23360,7 +23448,7 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
@@ -23375,7 +23463,7 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
@@ -23385,12 +23473,12 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
@@ -23589,11 +23677,15 @@
           <t>16.33</t>
         </is>
       </c>
-      <c r="CQ24" t="n">
-        <v>16.58</v>
-      </c>
-      <c r="CR24" t="n">
-        <v>17.19</v>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>16.58</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>17.19</t>
+        </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
@@ -24346,7 +24438,7 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
@@ -24361,22 +24453,22 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
@@ -24575,11 +24667,15 @@
           <t>16.365</t>
         </is>
       </c>
-      <c r="CQ25" t="n">
-        <v>16.63</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>17.2</v>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>16.63</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
@@ -25332,7 +25428,7 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
@@ -25347,22 +25443,22 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
@@ -25561,11 +25657,15 @@
           <t>16.39</t>
         </is>
       </c>
-      <c r="CQ26" t="n">
-        <v>16.68</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>17.21</v>
+      <c r="CQ26" t="inlineStr">
+        <is>
+          <t>16.68</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>17.21</t>
+        </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
@@ -26318,7 +26418,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -26333,22 +26433,22 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
@@ -26547,11 +26647,15 @@
           <t>16.405</t>
         </is>
       </c>
-      <c r="CQ27" t="n">
-        <v>16.74</v>
-      </c>
-      <c r="CR27" t="n">
-        <v>17.22</v>
+      <c r="CQ27" t="inlineStr">
+        <is>
+          <t>16.74</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>17.22</t>
+        </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
@@ -27304,7 +27408,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -27319,22 +27423,22 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
@@ -27533,11 +27637,15 @@
           <t>16.445</t>
         </is>
       </c>
-      <c r="CQ28" t="n">
-        <v>16.77</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>17.23</v>
+      <c r="CQ28" t="inlineStr">
+        <is>
+          <t>16.77</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>17.23</t>
+        </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
@@ -28290,7 +28398,7 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
@@ -28305,7 +28413,7 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
@@ -28315,12 +28423,12 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -28519,11 +28627,15 @@
           <t>54.77</t>
         </is>
       </c>
-      <c r="CQ29" t="n">
-        <v>55</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>55.56</v>
+      <c r="CQ29" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>55.56</t>
+        </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
@@ -29276,7 +29388,7 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
@@ -29291,7 +29403,7 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
@@ -29301,12 +29413,12 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
@@ -29505,11 +29617,15 @@
           <t>54.89</t>
         </is>
       </c>
-      <c r="CQ30" t="n">
-        <v>55.06</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>55.58</v>
+      <c r="CQ30" t="inlineStr">
+        <is>
+          <t>55.06</t>
+        </is>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>55.58</t>
+        </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
@@ -30262,7 +30378,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -30277,22 +30393,22 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
@@ -30491,11 +30607,15 @@
           <t>55.0</t>
         </is>
       </c>
-      <c r="CQ31" t="n">
-        <v>55.26</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>55.61</v>
+      <c r="CQ31" t="inlineStr">
+        <is>
+          <t>55.26</t>
+        </is>
+      </c>
+      <c r="CR31" t="inlineStr">
+        <is>
+          <t>55.61</t>
+        </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
@@ -31248,7 +31368,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -31263,22 +31383,22 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -31477,11 +31597,15 @@
           <t>55.11</t>
         </is>
       </c>
-      <c r="CQ32" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="CR32" t="n">
-        <v>55.62</v>
+      <c r="CQ32" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="CR32" t="inlineStr">
+        <is>
+          <t>55.62</t>
+        </is>
       </c>
       <c r="CS32" t="inlineStr">
         <is>
@@ -32234,7 +32358,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
@@ -32249,22 +32373,22 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -32463,11 +32587,15 @@
           <t>55.22000000000001</t>
         </is>
       </c>
-      <c r="CQ33" t="n">
-        <v>55.57</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>55.64</v>
+      <c r="CQ33" t="inlineStr">
+        <is>
+          <t>55.57</t>
+        </is>
+      </c>
+      <c r="CR33" t="inlineStr">
+        <is>
+          <t>55.64</t>
+        </is>
       </c>
       <c r="CS33" t="inlineStr">
         <is>
@@ -33220,7 +33348,7 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
@@ -33235,22 +33363,22 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
@@ -33449,11 +33577,15 @@
           <t>55.23</t>
         </is>
       </c>
-      <c r="CQ34" t="n">
-        <v>55.68</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>55.65</v>
+      <c r="CQ34" t="inlineStr">
+        <is>
+          <t>55.68</t>
+        </is>
+      </c>
+      <c r="CR34" t="inlineStr">
+        <is>
+          <t>55.65</t>
+        </is>
       </c>
       <c r="CS34" t="inlineStr">
         <is>
@@ -34206,7 +34338,7 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
@@ -34221,22 +34353,22 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
@@ -34435,11 +34567,15 @@
           <t>55.29</t>
         </is>
       </c>
-      <c r="CQ35" t="n">
-        <v>55.81</v>
-      </c>
-      <c r="CR35" t="n">
-        <v>55.66</v>
+      <c r="CQ35" t="inlineStr">
+        <is>
+          <t>55.81</t>
+        </is>
+      </c>
+      <c r="CR35" t="inlineStr">
+        <is>
+          <t>55.66</t>
+        </is>
       </c>
       <c r="CS35" t="inlineStr">
         <is>
@@ -35192,7 +35328,7 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
@@ -35207,22 +35343,22 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
@@ -35421,11 +35557,15 @@
           <t>55.34</t>
         </is>
       </c>
-      <c r="CQ36" t="n">
-        <v>55.91</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>55.72</v>
+      <c r="CQ36" t="inlineStr">
+        <is>
+          <t>55.91</t>
+        </is>
+      </c>
+      <c r="CR36" t="inlineStr">
+        <is>
+          <t>55.72</t>
+        </is>
       </c>
       <c r="CS36" t="inlineStr">
         <is>
@@ -36178,7 +36318,7 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
@@ -36193,22 +36333,22 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
@@ -36407,11 +36547,15 @@
           <t>55.30999999999999</t>
         </is>
       </c>
-      <c r="CQ37" t="n">
-        <v>55.98</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>55.78</v>
+      <c r="CQ37" t="inlineStr">
+        <is>
+          <t>55.98</t>
+        </is>
+      </c>
+      <c r="CR37" t="inlineStr">
+        <is>
+          <t>55.78</t>
+        </is>
       </c>
       <c r="CS37" t="inlineStr">
         <is>
